--- a/Team-Data/2013-14/3-15-2013-14.xlsx
+++ b/Team-Data/2013-14/3-15-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F2" t="n">
         <v>35</v>
       </c>
       <c r="G2" t="n">
-        <v>0.453</v>
+        <v>0.444</v>
       </c>
       <c r="H2" t="n">
         <v>48.4</v>
@@ -685,22 +752,22 @@
         <v>0.459</v>
       </c>
       <c r="L2" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="M2" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="N2" t="n">
-        <v>0.379</v>
+        <v>0.378</v>
       </c>
       <c r="O2" t="n">
         <v>16.8</v>
       </c>
       <c r="P2" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.777</v>
+        <v>0.781</v>
       </c>
       <c r="R2" t="n">
         <v>8.9</v>
@@ -718,37 +785,37 @@
         <v>15.3</v>
       </c>
       <c r="W2" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="X2" t="n">
         <v>4.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z2" t="n">
         <v>19</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>101.6</v>
+        <v>101.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF2" t="n">
         <v>18</v>
       </c>
       <c r="AG2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH2" t="n">
         <v>10</v>
@@ -772,19 +839,19 @@
         <v>5</v>
       </c>
       <c r="AO2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP2" t="n">
         <v>22</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AR2" t="n">
         <v>28</v>
       </c>
       <c r="AS2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT2" t="n">
         <v>28</v>
@@ -802,7 +869,7 @@
         <v>24</v>
       </c>
       <c r="AY2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ2" t="n">
         <v>4</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-15-2013-14</t>
+          <t>2014-03-15</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-4</v>
       </c>
       <c r="AD3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE3" t="n">
         <v>25</v>
@@ -942,7 +1009,7 @@
         <v>11</v>
       </c>
       <c r="AK3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AL3" t="n">
         <v>24</v>
@@ -966,7 +1033,7 @@
         <v>7</v>
       </c>
       <c r="AS3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT3" t="n">
         <v>14</v>
@@ -975,7 +1042,7 @@
         <v>25</v>
       </c>
       <c r="AV3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW3" t="n">
         <v>23</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-15-2013-14</t>
+          <t>2014-03-15</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E4" t="n">
         <v>33</v>
       </c>
       <c r="F4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>0.516</v>
+        <v>0.524</v>
       </c>
       <c r="H4" t="n">
         <v>48.4</v>
@@ -1043,31 +1110,31 @@
         <v>35.3</v>
       </c>
       <c r="J4" t="n">
-        <v>78.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="K4" t="n">
         <v>0.452</v>
       </c>
       <c r="L4" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M4" t="n">
         <v>22.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.367</v>
+        <v>0.365</v>
       </c>
       <c r="O4" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="P4" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.762</v>
+        <v>0.763</v>
       </c>
       <c r="R4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="S4" t="n">
         <v>29.3</v>
@@ -1088,22 +1155,22 @@
         <v>4</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z4" t="n">
         <v>22</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>97.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1.4</v>
+        <v>-1.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE4" t="n">
         <v>15</v>
@@ -1112,7 +1179,7 @@
         <v>14</v>
       </c>
       <c r="AG4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH4" t="n">
         <v>10</v>
@@ -1127,7 +1194,7 @@
         <v>14</v>
       </c>
       <c r="AL4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM4" t="n">
         <v>11</v>
@@ -1136,13 +1203,13 @@
         <v>13</v>
       </c>
       <c r="AO4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP4" t="n">
         <v>11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR4" t="n">
         <v>29</v>
@@ -1163,7 +1230,7 @@
         <v>6</v>
       </c>
       <c r="AX4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY4" t="n">
         <v>8</v>
@@ -1178,7 +1245,7 @@
         <v>22</v>
       </c>
       <c r="BC4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-15-2013-14</t>
+          <t>2014-03-15</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-1.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE5" t="n">
         <v>16</v>
@@ -1297,7 +1364,7 @@
         <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI5" t="n">
         <v>26</v>
@@ -1345,7 +1412,7 @@
         <v>29</v>
       </c>
       <c r="AX5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY5" t="n">
         <v>19</v>
@@ -1357,7 +1424,7 @@
         <v>10</v>
       </c>
       <c r="BB5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC5" t="n">
         <v>18</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-15-2013-14</t>
+          <t>2014-03-15</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E6" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F6" t="n">
         <v>29</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.554</v>
       </c>
       <c r="H6" t="n">
         <v>48.7</v>
@@ -1410,22 +1477,22 @@
         <v>80.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.431</v>
+        <v>0.432</v>
       </c>
       <c r="L6" t="n">
         <v>6.1</v>
       </c>
       <c r="M6" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0.346</v>
+        <v>0.347</v>
       </c>
       <c r="O6" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="P6" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="Q6" t="n">
         <v>0.774</v>
@@ -1437,7 +1504,7 @@
         <v>33</v>
       </c>
       <c r="T6" t="n">
-        <v>44.7</v>
+        <v>44.8</v>
       </c>
       <c r="U6" t="n">
         <v>22.4</v>
@@ -1449,13 +1516,13 @@
         <v>7.2</v>
       </c>
       <c r="X6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y6" t="n">
         <v>6.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AA6" t="n">
         <v>21.1</v>
@@ -1464,13 +1531,13 @@
         <v>93.40000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AE6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AF6" t="n">
         <v>13</v>
@@ -1509,7 +1576,7 @@
         <v>9</v>
       </c>
       <c r="AR6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AS6" t="n">
         <v>8</v>
@@ -1521,13 +1588,13 @@
         <v>11</v>
       </c>
       <c r="AV6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW6" t="n">
         <v>21</v>
       </c>
       <c r="AX6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY6" t="n">
         <v>29</v>
@@ -1542,7 +1609,7 @@
         <v>30</v>
       </c>
       <c r="BC6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-15-2013-14</t>
+          <t>2014-03-15</t>
         </is>
       </c>
     </row>
@@ -1649,19 +1716,19 @@
         <v>-4.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF7" t="n">
         <v>21</v>
       </c>
       <c r="AG7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI7" t="n">
         <v>23</v>
@@ -1679,10 +1746,10 @@
         <v>20</v>
       </c>
       <c r="AN7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO7" t="n">
         <v>16</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>17</v>
       </c>
       <c r="AP7" t="n">
         <v>18</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-15-2013-14</t>
+          <t>2014-03-15</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>1.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-15-2013-14</t>
+          <t>2014-03-15</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E9" t="n">
         <v>29</v>
       </c>
       <c r="F9" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G9" t="n">
-        <v>0.439</v>
+        <v>0.446</v>
       </c>
       <c r="H9" t="n">
         <v>48.2</v>
@@ -1965,31 +2032,31 @@
         <v>23.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0.36</v>
+        <v>0.361</v>
       </c>
       <c r="O9" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P9" t="n">
         <v>26.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.717</v>
+        <v>0.719</v>
       </c>
       <c r="R9" t="n">
         <v>12.3</v>
       </c>
       <c r="S9" t="n">
-        <v>33.2</v>
+        <v>33</v>
       </c>
       <c r="T9" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="U9" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="V9" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="W9" t="n">
         <v>7.3</v>
@@ -2007,13 +2074,13 @@
         <v>21.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>103.5</v>
+        <v>103.7</v>
       </c>
       <c r="AC9" t="n">
         <v>-2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AE9" t="n">
         <v>18</v>
@@ -2022,10 +2089,10 @@
         <v>19</v>
       </c>
       <c r="AG9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI9" t="n">
         <v>12</v>
@@ -2034,7 +2101,7 @@
         <v>5</v>
       </c>
       <c r="AK9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL9" t="n">
         <v>10</v>
@@ -2043,7 +2110,7 @@
         <v>9</v>
       </c>
       <c r="AN9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO9" t="n">
         <v>8</v>
@@ -2052,7 +2119,7 @@
         <v>5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR9" t="n">
         <v>5</v>
@@ -2061,13 +2128,13 @@
         <v>7</v>
       </c>
       <c r="AT9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU9" t="n">
         <v>12</v>
       </c>
       <c r="AV9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW9" t="n">
         <v>20</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-15-2013-14</t>
+          <t>2014-03-15</t>
         </is>
       </c>
     </row>
@@ -2117,34 +2184,34 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E10" t="n">
         <v>25</v>
       </c>
       <c r="F10" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>0.379</v>
+        <v>0.385</v>
       </c>
       <c r="H10" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="I10" t="n">
-        <v>38.8</v>
+        <v>38.9</v>
       </c>
       <c r="J10" t="n">
-        <v>86.7</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L10" t="n">
         <v>5.8</v>
       </c>
       <c r="M10" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="N10" t="n">
         <v>0.313</v>
@@ -2153,16 +2220,16 @@
         <v>17.2</v>
       </c>
       <c r="P10" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.671</v>
+        <v>0.669</v>
       </c>
       <c r="R10" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="S10" t="n">
-        <v>30.7</v>
+        <v>30.6</v>
       </c>
       <c r="T10" t="n">
         <v>45</v>
@@ -2174,7 +2241,7 @@
         <v>14.8</v>
       </c>
       <c r="W10" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="X10" t="n">
         <v>5.2</v>
@@ -2186,28 +2253,28 @@
         <v>20.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AB10" t="n">
         <v>100.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3</v>
+        <v>-2.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
       </c>
       <c r="AF10" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG10" t="n">
         <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
         <v>8</v>
@@ -2216,7 +2283,7 @@
         <v>4</v>
       </c>
       <c r="AK10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL10" t="n">
         <v>29</v>
@@ -2228,7 +2295,7 @@
         <v>29</v>
       </c>
       <c r="AO10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP10" t="n">
         <v>6</v>
@@ -2261,7 +2328,7 @@
         <v>18</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA10" t="n">
         <v>14</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-15-2013-14</t>
+          <t>2014-03-15</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2456,7 @@
         <v>8</v>
       </c>
       <c r="AH11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI11" t="n">
         <v>7</v>
@@ -2425,19 +2492,19 @@
         <v>3</v>
       </c>
       <c r="AT11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AU11" t="n">
         <v>8</v>
       </c>
       <c r="AV11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW11" t="n">
         <v>13</v>
       </c>
       <c r="AX11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-15-2013-14</t>
+          <t>2014-03-15</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>4.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AE12" t="n">
         <v>5</v>
@@ -2607,7 +2674,7 @@
         <v>4</v>
       </c>
       <c r="AT12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU12" t="n">
         <v>22</v>
@@ -2619,7 +2686,7 @@
         <v>17</v>
       </c>
       <c r="AX12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY12" t="n">
         <v>22</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-15-2013-14</t>
+          <t>2014-03-15</t>
         </is>
       </c>
     </row>
@@ -2663,61 +2730,61 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E13" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F13" t="n">
         <v>17</v>
       </c>
       <c r="G13" t="n">
-        <v>0.742</v>
+        <v>0.738</v>
       </c>
       <c r="H13" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="I13" t="n">
         <v>36.8</v>
       </c>
       <c r="J13" t="n">
-        <v>80.90000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L13" t="n">
         <v>6.8</v>
       </c>
       <c r="M13" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
       <c r="O13" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="P13" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.783</v>
+        <v>0.78</v>
       </c>
       <c r="R13" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S13" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="T13" t="n">
-        <v>45.4</v>
+        <v>45.1</v>
       </c>
       <c r="U13" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V13" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W13" t="n">
         <v>7</v>
@@ -2726,25 +2793,25 @@
         <v>5.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z13" t="n">
         <v>20.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>98.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC13" t="n">
         <v>6.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AE13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
         <v>2</v>
@@ -2753,13 +2820,13 @@
         <v>2</v>
       </c>
       <c r="AH13" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AI13" t="n">
         <v>22</v>
       </c>
       <c r="AJ13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK13" t="n">
         <v>12</v>
@@ -2771,7 +2838,7 @@
         <v>24</v>
       </c>
       <c r="AN13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO13" t="n">
         <v>11</v>
@@ -2780,7 +2847,7 @@
         <v>14</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR13" t="n">
         <v>22</v>
@@ -2789,13 +2856,13 @@
         <v>1</v>
       </c>
       <c r="AT13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AU13" t="n">
         <v>24</v>
       </c>
       <c r="AV13" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AW13" t="n">
         <v>24</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-15-2013-14</t>
+          <t>2014-03-15</t>
         </is>
       </c>
     </row>
@@ -2947,7 +3014,7 @@
         <v>3</v>
       </c>
       <c r="AL14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM14" t="n">
         <v>8</v>
@@ -2983,7 +3050,7 @@
         <v>7</v>
       </c>
       <c r="AX14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY14" t="n">
         <v>2</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-15-2013-14</t>
+          <t>2014-03-15</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-6.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
@@ -3138,7 +3205,7 @@
         <v>3</v>
       </c>
       <c r="AO15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP15" t="n">
         <v>19</v>
@@ -3174,7 +3241,7 @@
         <v>10</v>
       </c>
       <c r="BA15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB15" t="n">
         <v>12</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-15-2013-14</t>
+          <t>2014-03-15</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E16" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F16" t="n">
         <v>27</v>
       </c>
       <c r="G16" t="n">
-        <v>0.591</v>
+        <v>0.585</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
@@ -3227,10 +3294,10 @@
         <v>37.7</v>
       </c>
       <c r="J16" t="n">
-        <v>81.59999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.462</v>
+        <v>0.461</v>
       </c>
       <c r="L16" t="n">
         <v>5</v>
@@ -3239,19 +3306,19 @@
         <v>14.1</v>
       </c>
       <c r="N16" t="n">
-        <v>0.356</v>
+        <v>0.357</v>
       </c>
       <c r="O16" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="P16" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.748</v>
+        <v>0.749</v>
       </c>
       <c r="R16" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="S16" t="n">
         <v>30.8</v>
@@ -3263,40 +3330,40 @@
         <v>21.7</v>
       </c>
       <c r="V16" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="W16" t="n">
         <v>7.7</v>
       </c>
       <c r="X16" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AA16" t="n">
         <v>19</v>
       </c>
       <c r="AB16" t="n">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AE16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF16" t="n">
         <v>9</v>
       </c>
       <c r="AG16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH16" t="n">
         <v>16</v>
@@ -3317,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO16" t="n">
         <v>29</v>
@@ -3326,7 +3393,7 @@
         <v>28</v>
       </c>
       <c r="AQ16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR16" t="n">
         <v>14</v>
@@ -3344,13 +3411,13 @@
         <v>5</v>
       </c>
       <c r="AW16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX16" t="n">
         <v>14</v>
       </c>
       <c r="AY16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ16" t="n">
         <v>6</v>
@@ -3359,10 +3426,10 @@
         <v>29</v>
       </c>
       <c r="BB16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-15-2013-14</t>
+          <t>2014-03-15</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>5.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE17" t="n">
         <v>5</v>
@@ -3508,7 +3575,7 @@
         <v>15</v>
       </c>
       <c r="AQ17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-15-2013-14</t>
+          <t>2014-03-15</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E18" t="n">
         <v>13</v>
       </c>
       <c r="F18" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G18" t="n">
-        <v>0.197</v>
+        <v>0.2</v>
       </c>
       <c r="H18" t="n">
         <v>48.5</v>
@@ -3591,16 +3658,16 @@
         <v>35.6</v>
       </c>
       <c r="J18" t="n">
-        <v>82.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="K18" t="n">
         <v>0.431</v>
       </c>
       <c r="L18" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="M18" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="N18" t="n">
         <v>0.354</v>
@@ -3609,25 +3676,25 @@
         <v>16.2</v>
       </c>
       <c r="P18" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.757</v>
+        <v>0.758</v>
       </c>
       <c r="R18" t="n">
         <v>11.8</v>
       </c>
       <c r="S18" t="n">
-        <v>29.4</v>
+        <v>29.6</v>
       </c>
       <c r="T18" t="n">
-        <v>41.2</v>
+        <v>41.4</v>
       </c>
       <c r="U18" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="V18" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W18" t="n">
         <v>6.7</v>
@@ -3642,16 +3709,16 @@
         <v>20.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AB18" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>-8.199999999999999</v>
+        <v>-8</v>
       </c>
       <c r="AD18" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3681,7 +3748,7 @@
         <v>19</v>
       </c>
       <c r="AN18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO18" t="n">
         <v>25</v>
@@ -3693,7 +3760,7 @@
         <v>16</v>
       </c>
       <c r="AR18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS18" t="n">
         <v>28</v>
@@ -3702,7 +3769,7 @@
         <v>25</v>
       </c>
       <c r="AU18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV18" t="n">
         <v>18</v>
@@ -3711,10 +3778,10 @@
         <v>28</v>
       </c>
       <c r="AX18" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AY18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ18" t="n">
         <v>18</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-15-2013-14</t>
+          <t>2014-03-15</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3915,7 @@
         <v>24</v>
       </c>
       <c r="AI19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ19" t="n">
         <v>2</v>
@@ -3872,7 +3939,7 @@
         <v>3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR19" t="n">
         <v>2</v>
@@ -3881,7 +3948,7 @@
         <v>12</v>
       </c>
       <c r="AT19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU19" t="n">
         <v>6</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-15-2013-14</t>
+          <t>2014-03-15</t>
         </is>
       </c>
     </row>
@@ -4015,16 +4082,16 @@
         <v>-2.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AE20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF20" t="n">
         <v>20</v>
       </c>
       <c r="AG20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH20" t="n">
         <v>12</v>
@@ -4087,7 +4154,7 @@
         <v>20</v>
       </c>
       <c r="BB20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC20" t="n">
         <v>22</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-15-2013-14</t>
+          <t>2014-03-15</t>
         </is>
       </c>
     </row>
@@ -4119,28 +4186,28 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F21" t="n">
         <v>40</v>
       </c>
       <c r="G21" t="n">
-        <v>0.403</v>
+        <v>0.394</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
       </c>
       <c r="I21" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J21" t="n">
-        <v>83.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L21" t="n">
         <v>9.199999999999999</v>
@@ -4149,16 +4216,16 @@
         <v>24.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.372</v>
+        <v>0.371</v>
       </c>
       <c r="O21" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="P21" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.751</v>
+        <v>0.75</v>
       </c>
       <c r="R21" t="n">
         <v>11</v>
@@ -4170,19 +4237,19 @@
         <v>40.9</v>
       </c>
       <c r="U21" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V21" t="n">
         <v>13</v>
       </c>
       <c r="W21" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X21" t="n">
         <v>4.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Z21" t="n">
         <v>22.2</v>
@@ -4191,13 +4258,13 @@
         <v>19.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>98.90000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC21" t="n">
-        <v>-1.2</v>
+        <v>-1.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE21" t="n">
         <v>20</v>
@@ -4206,7 +4273,7 @@
         <v>21</v>
       </c>
       <c r="AG21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH21" t="n">
         <v>8</v>
@@ -4218,7 +4285,7 @@
         <v>14</v>
       </c>
       <c r="AK21" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AL21" t="n">
         <v>5</v>
@@ -4254,13 +4321,13 @@
         <v>2</v>
       </c>
       <c r="AW21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX21" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AY21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ21" t="n">
         <v>26</v>
@@ -4272,7 +4339,7 @@
         <v>20</v>
       </c>
       <c r="BC21" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-15-2013-14</t>
+          <t>2014-03-15</t>
         </is>
       </c>
     </row>
@@ -4379,16 +4446,16 @@
         <v>6.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AE22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF22" t="n">
         <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="n">
         <v>25</v>
@@ -4397,7 +4464,7 @@
         <v>4</v>
       </c>
       <c r="AJ22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK22" t="n">
         <v>4</v>
@@ -4409,7 +4476,7 @@
         <v>16</v>
       </c>
       <c r="AN22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO22" t="n">
         <v>5</v>
@@ -4433,7 +4500,7 @@
         <v>14</v>
       </c>
       <c r="AV22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW22" t="n">
         <v>10</v>
@@ -4442,7 +4509,7 @@
         <v>2</v>
       </c>
       <c r="AY22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ22" t="n">
         <v>25</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-15-2013-14</t>
+          <t>2014-03-15</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4667,7 @@
         <v>27</v>
       </c>
       <c r="AQ23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR23" t="n">
         <v>24</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-15-2013-14</t>
+          <t>2014-03-15</t>
         </is>
       </c>
     </row>
@@ -4665,28 +4732,28 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E24" t="n">
         <v>15</v>
       </c>
       <c r="F24" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G24" t="n">
-        <v>0.227</v>
+        <v>0.231</v>
       </c>
       <c r="H24" t="n">
         <v>48.5</v>
       </c>
       <c r="I24" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="J24" t="n">
         <v>88</v>
       </c>
       <c r="K24" t="n">
-        <v>0.431</v>
+        <v>0.432</v>
       </c>
       <c r="L24" t="n">
         <v>6.8</v>
@@ -4695,16 +4762,16 @@
         <v>22.1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.305</v>
+        <v>0.306</v>
       </c>
       <c r="O24" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="P24" t="n">
         <v>23.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.716</v>
+        <v>0.719</v>
       </c>
       <c r="R24" t="n">
         <v>11.8</v>
@@ -4716,34 +4783,34 @@
         <v>43.4</v>
       </c>
       <c r="U24" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="V24" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="W24" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X24" t="n">
         <v>3.9</v>
       </c>
       <c r="Y24" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AA24" t="n">
         <v>20.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>99.40000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>-11.5</v>
+        <v>-11.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4764,7 +4831,7 @@
         <v>1</v>
       </c>
       <c r="AK24" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL24" t="n">
         <v>23</v>
@@ -4776,19 +4843,19 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT24" t="n">
         <v>12</v>
@@ -4809,13 +4876,13 @@
         <v>30</v>
       </c>
       <c r="AZ24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA24" t="n">
         <v>11</v>
       </c>
       <c r="BB24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-15-2013-14</t>
+          <t>2014-03-15</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>2.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AE25" t="n">
         <v>11</v>
@@ -4937,7 +5004,7 @@
         <v>12</v>
       </c>
       <c r="AH25" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI25" t="n">
         <v>9</v>
@@ -4958,7 +5025,7 @@
         <v>10</v>
       </c>
       <c r="AO25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP25" t="n">
         <v>10</v>
@@ -4970,7 +5037,7 @@
         <v>13</v>
       </c>
       <c r="AS25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT25" t="n">
         <v>13</v>
@@ -4985,7 +5052,7 @@
         <v>9</v>
       </c>
       <c r="AX25" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AY25" t="n">
         <v>9</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-15-2013-14</t>
+          <t>2014-03-15</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>4.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
@@ -5119,7 +5186,7 @@
         <v>7</v>
       </c>
       <c r="AH26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI26" t="n">
         <v>3</v>
@@ -5143,7 +5210,7 @@
         <v>6</v>
       </c>
       <c r="AP26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-15-2013-14</t>
+          <t>2014-03-15</t>
         </is>
       </c>
     </row>
@@ -5211,85 +5278,85 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E27" t="n">
         <v>23</v>
       </c>
       <c r="F27" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G27" t="n">
-        <v>0.348</v>
+        <v>0.354</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
       </c>
       <c r="I27" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="J27" t="n">
-        <v>82.59999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="K27" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L27" t="n">
         <v>6.3</v>
       </c>
       <c r="M27" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="N27" t="n">
-        <v>0.335</v>
+        <v>0.337</v>
       </c>
       <c r="O27" t="n">
         <v>21</v>
       </c>
       <c r="P27" t="n">
-        <v>27.4</v>
+        <v>27.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.766</v>
+        <v>0.769</v>
       </c>
       <c r="R27" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="S27" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="T27" t="n">
-        <v>44.2</v>
+        <v>44</v>
       </c>
       <c r="U27" t="n">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="V27" t="n">
         <v>15.4</v>
       </c>
       <c r="W27" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X27" t="n">
         <v>4</v>
       </c>
       <c r="Y27" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z27" t="n">
         <v>22.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>101.1</v>
+        <v>101.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2.4</v>
+        <v>-2.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
@@ -5301,16 +5368,16 @@
         <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI27" t="n">
         <v>21</v>
       </c>
       <c r="AJ27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK27" t="n">
         <v>17</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>18</v>
       </c>
       <c r="AL27" t="n">
         <v>25</v>
@@ -5328,7 +5395,7 @@
         <v>4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR27" t="n">
         <v>6</v>
@@ -5343,16 +5410,16 @@
         <v>30</v>
       </c>
       <c r="AV27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW27" t="n">
         <v>19</v>
       </c>
       <c r="AX27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ27" t="n">
         <v>27</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-15-2013-14</t>
+          <t>2014-03-15</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>7.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5483,13 +5550,13 @@
         <v>1</v>
       </c>
       <c r="AH28" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI28" t="n">
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5531,7 +5598,7 @@
         <v>17</v>
       </c>
       <c r="AX28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY28" t="n">
         <v>16</v>
@@ -5540,7 +5607,7 @@
         <v>1</v>
       </c>
       <c r="BA28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB28" t="n">
         <v>7</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-15-2013-14</t>
+          <t>2014-03-15</t>
         </is>
       </c>
     </row>
@@ -5704,7 +5771,7 @@
         <v>16</v>
       </c>
       <c r="AU29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV29" t="n">
         <v>9</v>
@@ -5716,7 +5783,7 @@
         <v>22</v>
       </c>
       <c r="AY29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ29" t="n">
         <v>29</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-15-2013-14</t>
+          <t>2014-03-15</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-6</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE30" t="n">
         <v>25</v>
@@ -5847,13 +5914,13 @@
         <v>25</v>
       </c>
       <c r="AH30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI30" t="n">
         <v>27</v>
       </c>
       <c r="AJ30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK30" t="n">
         <v>23</v>
@@ -5865,7 +5932,7 @@
         <v>23</v>
       </c>
       <c r="AN30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO30" t="n">
         <v>23</v>
@@ -5874,7 +5941,7 @@
         <v>21</v>
       </c>
       <c r="AQ30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR30" t="n">
         <v>20</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-15-2013-14</t>
+          <t>2014-03-15</t>
         </is>
       </c>
     </row>
@@ -5939,25 +6006,25 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E31" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F31" t="n">
         <v>31</v>
       </c>
       <c r="G31" t="n">
-        <v>0.53</v>
+        <v>0.523</v>
       </c>
       <c r="H31" t="n">
         <v>49</v>
       </c>
       <c r="I31" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="J31" t="n">
-        <v>84.7</v>
+        <v>84.8</v>
       </c>
       <c r="K31" t="n">
         <v>0.455</v>
@@ -5966,31 +6033,31 @@
         <v>8.1</v>
       </c>
       <c r="M31" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="N31" t="n">
-        <v>0.386</v>
+        <v>0.387</v>
       </c>
       <c r="O31" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="P31" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.731</v>
+        <v>0.729</v>
       </c>
       <c r="R31" t="n">
         <v>11</v>
       </c>
       <c r="S31" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="T31" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="U31" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="V31" t="n">
         <v>14.6</v>
@@ -6002,37 +6069,37 @@
         <v>4.7</v>
       </c>
       <c r="Y31" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AB31" t="n">
         <v>100.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
       </c>
       <c r="AF31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH31" t="n">
         <v>1</v>
       </c>
       <c r="AI31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ31" t="n">
         <v>8</v>
@@ -6074,7 +6141,7 @@
         <v>13</v>
       </c>
       <c r="AW31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX31" t="n">
         <v>15</v>
@@ -6086,7 +6153,7 @@
         <v>16</v>
       </c>
       <c r="BA31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB31" t="n">
         <v>16</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-15-2013-14</t>
+          <t>2014-03-15</t>
         </is>
       </c>
     </row>
